--- a/AAII_Financials/Quarterly/JNJ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JNJ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
   <si>
     <t>JNJ</t>
   </si>
@@ -656,515 +656,527 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46201</v>
+      </c>
+      <c r="E7" s="2">
         <v>46110</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46019</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45928</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45837</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45746</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45655</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45564</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45200</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45109</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45018</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44927</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44836</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44745</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44654</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44563</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44472</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44381</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44290</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44199</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44101</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44010</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43919</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43828</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43737</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43464</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43282</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43191</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43009</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42918</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42827</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42736</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>25310000</v>
+      </c>
+      <c r="E8" s="3">
         <v>24062000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>24564000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>23993000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>23743000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>21893000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>22520000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>22471000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>22447000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>21383000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>21395000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>21351000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>21519000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>20894000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>19939000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>19996000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>40055000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>23426000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>24804000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>23338000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>23312000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>22321000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>22475000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>21082000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>18336000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>20691000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>20747000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>20729000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>20562000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>20021000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>20394000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>20348000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>20830000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>20009000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>20195000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>19650000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>18839000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>17766000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>18106000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>17820000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>8016000</v>
+      </c>
+      <c r="E9" s="3">
         <v>8086000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7812000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7291000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>7613000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>7349000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6908000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6757000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6867000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6504000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6515000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6380000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6462000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>6487000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6084000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>6172000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>12340000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>7582000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>7955000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>7250000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>7587000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>7063000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>7783000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>6940000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>6557000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>7047000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>7115000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>6847000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>6902000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>6592000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>6929000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>6566000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>6883000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>6608000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>7170000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>6920000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>5845000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>5409000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>5516000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>5483000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>17294000</v>
+      </c>
+      <c r="E10" s="3">
         <v>15976000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>16752000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>16702000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>16130000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>14544000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>15612000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>15714000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>15580000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>14879000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>14880000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>14971000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>15057000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>14407000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>13855000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>13824000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>27715000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>15844000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>16849000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>16088000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>15725000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>15258000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>14692000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>14142000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>11779000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>13644000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>13632000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>13882000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>13660000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>13429000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>13465000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>13782000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>13947000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>13401000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>13025000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>12730000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>12994000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>12357000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>12590000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>12337000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1207,130 +1219,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>3653000</v>
+      </c>
+      <c r="E12" s="3">
         <v>3527000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>4252000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>3672000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>3516000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>3225000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>5298000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>4952000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3440000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3542000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>4480000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3447000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3703000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3455000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>3710000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>3485000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>6940000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>3462000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>4720000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>3422000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>3394000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>3178000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>4032000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>2840000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>2707000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>2580000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>3232000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>2599000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>2666000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>2858000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>3224000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>2508000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>2639000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>2404000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>7278000</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>5158000</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>4582000</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>2075000</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>2640000</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>2179000</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1451,175 +1467,181 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>676000</v>
+      </c>
+      <c r="E14" s="3">
         <v>416000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1063000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-225000</v>
       </c>
-      <c r="G14" s="3">
-        <v>480000</v>
-      </c>
       <c r="H14" s="3">
+        <v>479000</v>
+      </c>
+      <c r="I14" s="3">
         <v>-6920000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>458000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2747000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1383000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2971000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>772000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1490000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>245000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>7948000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2462000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>506000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1488000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1382000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1234000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>3072000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>68000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-533000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>2921000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1668000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>721000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-782000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>206000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>128000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>142000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>980000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>227000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>1316000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>176000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>107000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>1003000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>187000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>128000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>161000</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>298000</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>109000</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>1959000</v>
+      </c>
+      <c r="E15" s="3">
         <v>2004000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2011000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1777000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1943000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1772000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1896000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1846000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1782000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1815000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1460000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1829000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1934000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1880000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1695,8 +1717,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,252 +1761,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>17922000</v>
+      </c>
+      <c r="E17" s="3">
         <v>17467000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>18677000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>16747000</v>
       </c>
-      <c r="G17" s="3">
-        <v>16880000</v>
-      </c>
       <c r="H17" s="3">
+        <v>16881000</v>
+      </c>
+      <c r="I17" s="3">
         <v>15555000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>18432000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>16962000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>15753000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>15073000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>16559000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>14970000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>15201000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>14495000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>16099000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>14824000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>29708000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>17564000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>19968000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>19489000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>16650000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>14892000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>20828000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>16681000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>14396000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>14182000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>16529000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>19082000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>13521000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>15599000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>17272000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>15925000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>15857000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>14528000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>17635000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>14860000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>14091000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>12191000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>13782000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>12539000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>7388000</v>
+      </c>
+      <c r="E18" s="3">
         <v>6595000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5887000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>7246000</v>
       </c>
-      <c r="G18" s="3">
-        <v>6863000</v>
-      </c>
       <c r="H18" s="3">
+        <v>6862000</v>
+      </c>
+      <c r="I18" s="3">
         <v>6338000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4088000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5509000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>6694000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>6310000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4836000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>6381000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>6318000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>6399000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3840000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>5172000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>10347000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>5862000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>4836000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3849000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>6662000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>7429000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1647000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>4401000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3940000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>6509000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>4218000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1647000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>7041000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>4422000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3122000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>4423000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>4973000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>5481000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>2560000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>4790000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>4748000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>5575000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>4324000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>5281000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2024,53 +2056,54 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-97000</v>
+      </c>
+      <c r="E20" s="3">
         <v>146000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-119000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-40000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-156000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-245000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-113000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-477000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-312000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-166000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-550000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-144000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-124000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-276000</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -2146,175 +2179,181 @@
       <c r="AP20" s="3">
         <v>0</v>
       </c>
+      <c r="AQ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>9444000</v>
+      </c>
+      <c r="E21" s="3">
         <v>8453000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>8017000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>9063000</v>
       </c>
-      <c r="G21" s="3">
-        <v>8962000</v>
-      </c>
       <c r="H21" s="3">
+        <v>8961000</v>
+      </c>
+      <c r="I21" s="3">
         <v>8355000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>6097000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>7832000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>8788000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>8291000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>6846000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>8354000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>8376000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>8555000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5612000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>6857000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>13860000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>7631000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>6679000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>5663000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>8501000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>9323000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>3587000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>6219000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>5666000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>8256000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>6034000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>3374000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>8746000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>6183000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>4857000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>6154000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>6690000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>7227000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>4429000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>6501000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>5898000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>6487000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>5379000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>6189000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>281000</v>
+      </c>
+      <c r="E22" s="3">
         <v>272000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>214000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>245000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>308000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>204000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>137000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>193000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>270000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>155000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>151000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>192000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>217000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>212000</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
@@ -2390,252 +2429,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>6747000</v>
+      </c>
+      <c r="E23" s="3">
         <v>5990000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4966000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>7493000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>6491000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>13631000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3887000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3338000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5748000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3714000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4826000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5217000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6306000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1287000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3840000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>5172000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>10347000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>5862000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>4836000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>3849000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>6662000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>7429000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1647000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4401000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>3940000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>6509000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>4218000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1647000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>7041000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>4422000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>3122000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>4423000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>4973000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>5481000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>2560000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>4790000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>4748000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>5575000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>4324000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>5281000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>1213000</v>
+      </c>
+      <c r="E24" s="3">
         <v>755000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-150000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2341000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>954000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2632000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>456000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>644000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1062000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>459000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>694000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>908000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>930000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-796000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>613000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>862000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1514000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>713000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>100000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>182000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>384000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1232000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-91000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>847000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>314000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1013000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>208000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-106000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1434000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>673000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>80000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>489000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1019000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>1114000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>273000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>1026000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>921000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>1153000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>510000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>1009000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2756,252 +2804,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>5534000</v>
+      </c>
+      <c r="E26" s="3">
         <v>5235000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>5116000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>5152000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>5537000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>10999000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3431000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2694000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4686000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3255000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4132000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4309000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5376000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-491000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3227000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>4310000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>8833000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>5149000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4736000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>3667000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>6278000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>6197000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1738000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3554000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>3626000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>5496000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>4010000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1753000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>5607000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>3749000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>3042000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>3934000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>3954000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>4367000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>2287000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>3764000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>3827000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>4422000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>3814000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>4272000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>5534000</v>
+      </c>
+      <c r="E27" s="3">
         <v>5235000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>5116000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>5152000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>5537000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>10999000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3431000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2694000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4686000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3255000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4049000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>26028000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5144000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-68000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3227000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>4310000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>8833000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>5149000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>4736000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>3667000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>6278000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>6197000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1738000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3554000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>3626000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>5496000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>4010000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1753000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>5607000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>3749000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>3042000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>3934000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>3954000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>4367000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>2287000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>3764000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>3827000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>4422000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>3814000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>4272000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3122,8 +3179,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3155,34 +3215,34 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-83000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>21719000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-232000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>423000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>293000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>148000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>1130000</v>
       </c>
-      <c r="T29" s="3" t="s">
+      <c r="U29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>24</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>24</v>
@@ -3190,20 +3250,20 @@
       <c r="X29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3" t="s">
+      <c r="Y29" s="3" t="s">
         <v>24</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC29" s="3">
         <v>300000</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>24</v>
@@ -3226,11 +3286,11 @@
       <c r="AJ29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-13000000</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>24</v>
@@ -3244,8 +3304,11 @@
       <c r="AP29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3366,8 +3429,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3488,53 +3554,56 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>97000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-146000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>119000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>40000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>156000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>245000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>113000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>477000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>312000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>166000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>550000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>144000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>124000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>276000</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -3610,130 +3679,136 @@
       <c r="AP32" s="3">
         <v>0</v>
       </c>
+      <c r="AQ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5534000</v>
+      </c>
+      <c r="E33" s="3">
         <v>5235000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>5116000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>5152000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>5537000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>10999000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3431000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2694000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4686000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3255000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4049000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>26028000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5144000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-68000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3520000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>4458000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>9963000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>5149000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>4736000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>3667000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>6278000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>6197000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1738000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3554000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>3626000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>5796000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>4010000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1753000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>5607000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>3749000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>3042000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>3934000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>3954000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>4367000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-10713000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>3764000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>3827000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>4422000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>3814000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>4272000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3854,257 +3929,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5534000</v>
+      </c>
+      <c r="E35" s="3">
         <v>5235000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>5116000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>5152000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>5537000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>10999000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3431000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2694000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4686000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3255000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4049000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>26028000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5144000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-68000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3520000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>4458000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>9963000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>5149000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>4736000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>3667000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>6278000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>6197000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1738000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3554000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>3626000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>5796000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>4010000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1753000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>5607000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>3749000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>3042000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>3934000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>3954000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>4367000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-10713000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>3764000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>3827000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>4422000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>3814000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>4272000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46201</v>
+      </c>
+      <c r="E38" s="2">
         <v>46110</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46019</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45928</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45837</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45746</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45655</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45564</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45200</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45109</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45018</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44927</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44836</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44745</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44654</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44563</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44472</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44381</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44290</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44199</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44101</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44010</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43919</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43828</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43737</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43464</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43282</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43191</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43009</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42918</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42827</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42736</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4147,8 +4231,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4191,496 +4276,509 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>20422000</v>
+      </c>
+      <c r="E41" s="3">
         <v>21688000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>19709000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>18231000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>18577000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>38474000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>24105000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>19980000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>24878000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>25473000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>21859000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>19728000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>21183000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>19170000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>10294000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5553000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5305000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4707000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4837000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4727000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4931000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4341000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4965000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>10716000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3743000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4923000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5501000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4148000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3983000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>6973000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>18107000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>16056000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>17569000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>14639000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>17824000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>15721000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>12598000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>20909000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>18972000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>18205000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>336000</v>
+      </c>
+      <c r="E42" s="3">
         <v>363000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>393000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>331000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>303000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>307000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>417000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>317000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>597000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>745000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1068000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>3783000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>7322000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>5443000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>13225000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>28526000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>27263000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>25681000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>26771000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>26274000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>20375000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>20278000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>20220000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>20065000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>15392000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>13101000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>13786000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>13797000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>11295000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>8363000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1580000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>3308000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>570000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>565000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>472000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>510000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>255000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>18434000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>22935000</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>22228000</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>19046000</v>
+      </c>
+      <c r="E43" s="3">
         <v>17721000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>17178000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>17611000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>17846000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>16020000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>14842000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>16174000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>15794000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>14946000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>14873000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>14798000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>16777000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>16350000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>16160000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>15890000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>16139000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>15594000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>15283000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>14911000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>14871000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>14938000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>13576000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>14579000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>14645000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>14874000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>14481000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>14801000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>14653000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>14115000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>14098000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>14048000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>14111000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>14166000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>13490000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>13155000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>13283000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>12300000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>11699000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>11798000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>15144000</v>
+      </c>
+      <c r="E44" s="3">
         <v>14583000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>14191000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>14146000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>13412000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>12659000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>12444000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>12603000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>12169000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>11383000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>11181000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>11198000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>12888000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>12809000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>12483000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>11675000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>11437000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>10990000</v>
-      </c>
-      <c r="U44" s="3">
-        <v>10387000</v>
       </c>
       <c r="V44" s="3">
         <v>10387000</v>
       </c>
       <c r="W44" s="3">
+        <v>10387000</v>
+      </c>
+      <c r="X44" s="3">
         <v>10100000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>9952000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>9344000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>9599000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>9424000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>8868000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>9020000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>9173000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>9263000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>9086000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>8599000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>8678000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>8810000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>9014000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>8765000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>9521000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>9699000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>8878000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>8144000</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>8488000</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4723,313 +4821,319 @@
       <c r="P45" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R45" s="3">
         <v>3132000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3592000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3703000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3452000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3701000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3590000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3492000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3024000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3132000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2619000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2688000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2460000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2486000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2414000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2605000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3450000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3649000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>5104000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>4378000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>4384000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>2537000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>2922000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>2954000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>2826000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>3282000</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>2600000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>59774000</v>
+      </c>
+      <c r="E46" s="3">
         <v>59173000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>55624000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>54611000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>54498000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>71551000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>55893000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>53249000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>57817000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>57002000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>53495000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>53703000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>60567000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>64388000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>55294000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>65236000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>63847000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>60424000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>60979000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>59889000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>53769000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>52533000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>51237000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>57578000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>45892000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>44226000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>45274000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>44333000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>41799000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>41987000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>46033000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>47194000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>45438000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>42768000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>43088000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>41829000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>38789000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>63347000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>65032000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>63319000</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1635000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1591000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1575000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1452000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1276000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1258000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>5524000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1277000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1143000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>5193000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>9069000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4708000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1240000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1229000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>576000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1884000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1340000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1452000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1884000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1867000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1678000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1452000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1481000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1140000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1488000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>826000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1148000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>863000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>963000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>830000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>511000</v>
-      </c>
-      <c r="AH47" s="3">
-        <v>697000</v>
       </c>
       <c r="AI47" s="3">
         <v>697000</v>
       </c>
       <c r="AJ47" s="3">
+        <v>697000</v>
+      </c>
+      <c r="AK47" s="3">
         <v>731000</v>
       </c>
-      <c r="AK47" s="3">
-        <v>0</v>
-      </c>
       <c r="AL47" s="3">
         <v>0</v>
       </c>
@@ -5045,252 +5149,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>23582000</v>
+      </c>
+      <c r="E48" s="3">
         <v>23270000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>24469000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>22338000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>21949000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>20871000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>21618000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>20479000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>19748000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>19632000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>20898000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>18821000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>20576000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>20174000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>20903000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>18152000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>18354000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>18701000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>19862000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>18478000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>18632000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>18367000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>19766000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>17855000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>17598000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>17401000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>18615000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>18011000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>18228000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>17879000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>17035000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>16629000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>16632000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>17040000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>17005000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>16628000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>16458000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>16191000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>15912000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>16095000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>96708000</v>
+      </c>
+      <c r="E49" s="3">
         <v>97619000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>99175000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>96785000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>97952000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>81223000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>81818000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>84289000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>83975000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>70902000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>70733000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>71145000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>91686000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>93023000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>93556000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>73719000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>76574000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>79355000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>81638000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>83345000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>86063000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>86798000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>89795000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>81313000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>81303000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>80809000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>81282000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>81137000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>82993000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>78348000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>78064000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>79339000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>80402000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>83514000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>85134000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>85877000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>86176000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>54310000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>49681000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>50813000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5411,8 +5524,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5533,130 +5649,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>12634000</v>
+      </c>
+      <c r="E52" s="3">
         <v>12514000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>11493000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>10964000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>10913000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>10276000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4790000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>9644000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>9401000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>8932000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4084000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>8425000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>8838000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>8338000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>17049000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>16133000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>17609000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>18423000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>17655000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>15649000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>16298000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>13407000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>12615000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>12807000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>12099000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>11755000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>11409000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>11177000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>11134000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>10983000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>11311000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>11844000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>12196000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>12572000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>12076000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>11324000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>11384000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>11070000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>10583000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>10142000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5777,130 +5899,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>201061000</v>
+      </c>
+      <c r="E54" s="3">
         <v>200894000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>199210000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>192816000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>193389000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>193671000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>180104000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>178287000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>181088000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>171966000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>167558000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>166061000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>191686000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>195969000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>187378000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>175124000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>177724000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>178355000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>182018000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>179228000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>176440000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>172557000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>174894000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>170693000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>158380000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>155017000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>157728000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>155521000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>155117000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>150027000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>152954000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>155703000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>155365000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>156625000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>157303000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>155658000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>152807000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>144918000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>141208000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>140369000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5943,8 +6071,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5987,740 +6116,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9223000</v>
+      </c>
+      <c r="E57" s="3">
         <v>10460000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11991000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>9625000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>9464000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>9545000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>10311000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8954000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8848000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8174000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>9632000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8355000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10443000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>9909000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>11703000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>10153000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>9765000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>9309000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>11055000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>8961000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>8704000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>8503000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>9505000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>7044000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>6765000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>7411000</v>
       </c>
-      <c r="AC57" s="3" t="s">
+      <c r="AD57" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>7491000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>6912000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>6923000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>7537000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>7000000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>6516000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>6443000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>7310000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>6390000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>6135000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>6082000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>6918000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>5971000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>11692000</v>
+      </c>
+      <c r="E58" s="3">
         <v>17460000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>8495000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6387000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>11526000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>13897000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5983000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4462000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>9855000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>8550000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3451000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3870000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>11701000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>17979000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>12771000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>4424000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>4305000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>4297000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3766000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3798000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3173000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3350000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2631000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>5078000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>5332000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2190000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1202000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1799000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1220000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1208000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2796000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1171000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>2078000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>2696000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>3906000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>8491000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>7209000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>5355000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>4684000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>3443000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1051000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1087000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1388000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1928000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1665000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4217000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3772000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4834000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4309000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3318000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2993000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2899000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2687000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4266000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>31328000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>30966000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>30751000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>29784000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>30405000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>31802000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>26844000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>29079000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>30357000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>26725000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>24675000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>24088000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>34762000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>25872000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>23221000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>20980000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>20897000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>19266000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>18894000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>17942000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>19321000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>16925000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>15528000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>13682000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>14685000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>13816000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>54895000</v>
+      </c>
+      <c r="E60" s="3">
         <v>57716000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>54126000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>50869000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>54180000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>56903000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>50321000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>51759000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>53933000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>48725000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>46282000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>44370000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>54170000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>60373000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>55802000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>45543000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>44821000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>43390000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>45226000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>44561000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>38721000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>40932000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>42493000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>38847000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>36772000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>33689000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>35964000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>35162000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>31353000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>29111000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>31230000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>27437000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>27488000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>27081000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>30537000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>31806000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>28872000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>25119000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>26287000</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>23230000</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>37344000</v>
+      </c>
+      <c r="E61" s="3">
         <v>37527000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>40838000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>39408000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>39235000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>38355000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>31851000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>31289000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>31636000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>25082000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>26981000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>26051000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>33901000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>34928000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>26888000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>27603000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>28292000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>28851000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>29985000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>30130000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>30310000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>30263000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>32635000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>32680000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>25062000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>25393000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>26494000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>26919000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>27699000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>27660000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>27684000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>29480000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>29405000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>29837000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>30675000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>26675000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>27363000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>27015000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>22442000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>23546000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>10586000</v>
+      </c>
+      <c r="E62" s="3">
         <v>10694000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>8954000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>10344000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>10681000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>10830000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>16739000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>15277000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>14427000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>17948000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>15179000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>16102000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>17118000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>18717000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>27884000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>27379000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>28254000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>31405000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>32784000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>34265000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>37829000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>35528000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>36488000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>34693000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>33568000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>34641000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>35799000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>35230000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>35280000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>34301000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>34288000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>34160000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>35583000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>36452000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>35931000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>23198000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>24650000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>22443000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>22061000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>20824000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6841,8 +6989,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6963,8 +7114,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7085,130 +7239,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>116090000</v>
+      </c>
+      <c r="E66" s="3">
         <v>119708000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>117666000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>113539000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>114916000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>115562000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>108614000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>108129000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>109550000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>101946000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>98784000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>94833000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>115277000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>125100000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>110574000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>100525000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>101367000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>103646000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>107995000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>108956000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>106860000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>106723000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>111616000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>106220000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>95402000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>93723000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>98257000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>97311000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>94332000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>91072000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>93202000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>91077000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>92476000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>93370000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>97143000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>81679000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>80885000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>74577000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>70790000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>67600000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7251,8 +7411,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7373,8 +7534,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7495,8 +7659,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7617,8 +7784,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7739,130 +7909,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>171665000</v>
+      </c>
+      <c r="E72" s="3">
         <v>169161000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>168978000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>167281000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>165371000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>162635000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>155791000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>155179000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>155360000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>153378000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>153843000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>152536000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>129381000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>124558000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>128345000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>127917000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>126216000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>124380000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>123060000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>121092000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>120154000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>116508000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>113890000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>114831000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>113898000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>112901000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>110659000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>109242000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>109809000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>106650000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>106216000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>107617000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>106123000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>104339000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>101793000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>114805000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>113208000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>111643000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>110551000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>108860000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7983,8 +8159,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8105,8 +8284,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8227,130 +8409,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>84971000</v>
+      </c>
+      <c r="E76" s="3">
         <v>81186000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>81544000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>79277000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>78473000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>78109000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>71490000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>70158000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>71538000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>70020000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>68774000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>71228000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>75149000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>70869000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>76804000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>74599000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>76357000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>74709000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>74023000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>70272000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>69580000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>65834000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>63278000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>64473000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>62978000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>61294000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>59471000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>58210000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>60785000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>58955000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>59752000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>64626000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>62889000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>63255000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>60160000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>73979000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>71922000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>70341000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>70418000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>72769000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8471,257 +8659,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46201</v>
+      </c>
+      <c r="E80" s="2">
         <v>46110</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46019</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45928</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45837</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45746</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45655</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45564</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45200</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45109</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45018</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44927</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44836</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44745</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44654</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44563</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44472</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44381</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44290</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44199</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44101</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44010</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43919</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43828</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43737</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43464</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43282</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43191</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43009</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42918</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42827</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42736</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5534000</v>
+      </c>
+      <c r="E81" s="3">
         <v>5235000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>5116000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>5152000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>5537000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>10999000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3431000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2694000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4686000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3255000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4049000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>26028000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5144000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-68000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3520000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>4458000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>9963000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>5149000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>4736000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>3667000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>6278000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>6197000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1738000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3554000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>3626000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>5796000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>4010000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1753000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>5607000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>3749000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>3042000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>3934000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>3954000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>4367000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-10713000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>3764000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>3827000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>4422000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>3814000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>4272000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8764,130 +8961,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>643000</v>
+      </c>
+      <c r="E83" s="3">
         <v>672000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>796000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>646000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>682000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>715000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>360000</v>
       </c>
-      <c r="J83" s="3" t="s">
+      <c r="K83" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>834000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>780000</v>
       </c>
-      <c r="M83" s="3" t="s">
+      <c r="N83" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>885000</v>
       </c>
-      <c r="O83" s="3" t="s">
+      <c r="P83" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>669000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1772000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1685000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>3513000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1769000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1843000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1814000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1839000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1894000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1940000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1818000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1726000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>1747000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>1816000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>1727000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>1705000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>1761000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>1735000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>1731000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>1717000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>1746000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>1869000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>1711000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>1150000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>912000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>1055000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>908000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9008,8 +9209,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9130,8 +9334,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9252,8 +9459,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9374,8 +9584,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9496,130 +9709,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>8616000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2514000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>7309000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>9169000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3878000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4174000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>6983000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>7993000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5633000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3657000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>7863000</v>
       </c>
-      <c r="N89" s="3" t="s">
+      <c r="O89" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4182000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3257000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>5350000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>6284000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>9560000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3979000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>5732000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>8290000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>5314000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>4074000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>8343000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>8383000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3452000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>3358000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>6398000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>7527000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>5948000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>3543000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>6244000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>6272000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>6079000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>3606000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>6105000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>6266000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>5772000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>2913000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>6653000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>5361000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9662,130 +9881,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1321000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1049000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1837000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1157000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1043000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-795000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1612000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1029000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-976000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-807000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1589000</v>
       </c>
-      <c r="N91" s="3" t="s">
+      <c r="O91" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1124000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-863000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1587000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-952000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-863000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-607000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1415000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-747000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-813000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-677000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1323000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-737000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-662000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-625000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1260000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-745000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-837000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-656000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1318000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-819000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-875000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-658000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-1240000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-790000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-689000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-560000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-1093000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-737000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9906,8 +10129,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10028,130 +10254,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1110000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1040000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4485000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-542000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-18264000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-297000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1320000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3128000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-13687000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-464000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1202000</v>
       </c>
-      <c r="N94" s="3" t="s">
+      <c r="O94" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3776000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>3315000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4397000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1701000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-6273000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3634000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-5360000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2719000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-419000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-185000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-7903000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-4819000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-7522000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-581000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1344000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1645000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1788000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1417000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>2228000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-4269000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-201000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-925000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-505000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1180000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-12247000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-936000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-2174000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-2372000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10194,64 +10426,65 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>3131000</v>
+        <v>3227000</v>
       </c>
       <c r="E96" s="3">
         <v>3131000</v>
       </c>
       <c r="F96" s="3">
+        <v>3131000</v>
+      </c>
+      <c r="G96" s="3">
         <v>3132000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>3129000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>2989000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>2984000</v>
-      </c>
-      <c r="J96" s="3">
-        <v>2985000</v>
       </c>
       <c r="K96" s="3">
         <v>2985000</v>
       </c>
       <c r="L96" s="3">
+        <v>2985000</v>
+      </c>
+      <c r="M96" s="3">
         <v>2869000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>2865000</v>
       </c>
-      <c r="N96" s="3" t="s">
+      <c r="O96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>3092000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>2942000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-2954000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-2970000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-5758000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-2787000</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-2791000</v>
       </c>
       <c r="V96" s="3">
         <v>-2791000</v>
@@ -10260,64 +10493,67 @@
         <v>-2791000</v>
       </c>
       <c r="X96" s="3">
+        <v>-2791000</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-2659000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-2658000</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-2659000</v>
       </c>
       <c r="AA96" s="3">
         <v>-2659000</v>
       </c>
       <c r="AB96" s="3">
+        <v>-2659000</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-2505000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-2500000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-2499000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-2522000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-2396000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-2411000</v>
-      </c>
-      <c r="AH96" s="3">
-        <v>-2415000</v>
       </c>
       <c r="AI96" s="3">
         <v>-2415000</v>
       </c>
       <c r="AJ96" s="3">
+        <v>-2415000</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-2253000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-2256000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-2254000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-2262000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-2171000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-2170000</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-2185000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10438,8 +10674,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10560,8 +10799,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10682,370 +10924,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-8777000</v>
+      </c>
+      <c r="E100" s="3">
         <v>530000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1369000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-8927000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-5665000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>10422000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1340000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-9882000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>7544000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>546000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4655000</v>
       </c>
-      <c r="N100" s="3" t="s">
+      <c r="O100" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-5991000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>6138000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1700000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-3925000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-6646000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-4385000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-3436000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-2207000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-3279000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-5125000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-5644000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>4196000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-357000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-4315000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-4072000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-3893000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-4534000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-5516000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-6389000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-3477000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-2674000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-5970000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-3537000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-2069000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-1917000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-150000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-3464000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-3445000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>154000</v>
+      </c>
+      <c r="E101" s="3">
         <v>70000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-198000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>119000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-85000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-125000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>125000</v>
       </c>
-      <c r="J101" s="3" t="s">
+      <c r="K101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-97000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>28000</v>
       </c>
-      <c r="M101" s="3" t="s">
+      <c r="N101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-286000</v>
       </c>
-      <c r="O101" s="3" t="s">
+      <c r="P101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>16000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>119000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-286000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-145000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>16000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-53000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-92000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>45000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-78000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>224000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>31000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>71000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-237000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>74000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-116000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>16000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>17000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-32000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-39000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-274000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>104000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>40000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>106000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>81000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>110000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-248000</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1266000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1979000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1478000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-346000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-19897000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>14369000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>4125000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4898000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-595000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3614000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2131000</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>-5682000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>12738000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2772000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>372000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-3504000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-4024000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-3117000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>3272000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1661000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1314000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-4980000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>7791000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-4356000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1775000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1056000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1873000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-358000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-3373000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>2051000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-1513000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>2930000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-3185000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>2103000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>3123000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-8311000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>1937000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>767000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-435000</v>
       </c>
     </row>
